--- a/data/trans_orig/cron_mort_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la mortalidad</t>
+          <t>Índice de cronicidad física en base a la mortalidad (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,15</t>
+          <t>0,03; 0,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +741,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,02</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,01</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,01</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,01</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,03; 0,11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,01</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,01</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,01</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,11</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,5</t>
+          <t>0,06; 0,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,35</t>
+          <t>0,07; 0,36</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,04</t>
+          <t>0,01; 0,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,04; 0,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,18</t>
+          <t>0,06; 0,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,05; 0,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,15</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,18</t>
+          <t>0,11; 0,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,13; 0,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,15</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,17</t>
+          <t>0,12; 0,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,3</t>
+          <t>0,25; 0,31</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,24</t>
+          <t>0,15; 0,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,36</t>
+          <t>0,25; 0,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,53</t>
+          <t>0,42; 0,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,33</t>
+          <t>0,23; 0,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,38</t>
+          <t>0,12; 0,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,32</t>
+          <t>0,26; 0,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,43</t>
+          <t>0,17; 0,43</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,26</t>
+          <t>0,15; 0,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,44</t>
+          <t>0,33; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,26</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,37</t>
+          <t>0,27; 0,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">

--- a/data/trans_orig/cron_mort_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Edad-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,16</t>
+          <t>0,03; 0,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,11</t>
+          <t>0,04; 0,1</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,14</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,51</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,36</t>
+          <t>0,06; 0,1</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1006,39 +1006,39 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,01; 0,04</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,11</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,02</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,02; 0,05</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,02; 0,04</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,11</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>0,01; 0,03</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,02</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,05</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 0,04</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 0,03</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0,02; 0,03</t>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1136,49 +1136,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,07</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,07</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 0,2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,03; 0,06</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,07</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0,05; 0,09</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,08</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 0,17</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0,03; 0,06</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,09</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,08</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 0,17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,06</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0,05; 0,07</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,14; 0,18</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,17</t>
+          <t>0,11; 0,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,2</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,31</t>
+          <t>0,25; 0,3</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,35</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,54</t>
+          <t>0,4; 0,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,19; 0,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,34</t>
+          <t>0,24; 0,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,39</t>
+          <t>0,34; 0,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,33</t>
+          <t>0,25; 0,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,43</t>
+          <t>0,38; 0,45</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,25</t>
+          <t>0,15; 0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,38</t>
+          <t>0,26; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,79</t>
+          <t>0,64; 0,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,38</t>
+          <t>0,27; 0,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,37</t>
+          <t>0,29; 0,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,39</t>
+          <t>0,3; 0,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1643,47 +1643,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,2; 0,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,22; 0,24</t>
         </is>
       </c>
     </row>
